--- a/Hemapreetha_Timesheet_1May-31May.xlsx
+++ b/Hemapreetha_Timesheet_1May-31May.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gunas\Hema\git-my\vinove\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48DCCB98-63D1-46CA-AA01-A6A75BFB0DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93BE19B4-410A-429E-8BCA-233E4F8E0CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
   <si>
     <t>Monthly Timesheet</t>
   </si>
@@ -121,6 +121,76 @@
   </si>
   <si>
     <t>5/31/2025</t>
+  </si>
+  <si>
+    <t>Congressional Communities
+==================================
+Find CC result Page spacing changes responive view design - Done
+Find CC page responive view design - Done
+My account page responive view design changes - Done</t>
+  </si>
+  <si>
+    <t>Congressional Communities
+==================================
+Donate page responive view design - Done
+About us page responive view design - Done
+My account page responive view design changes - Done</t>
+  </si>
+  <si>
+    <t>Congressional Communities
+==================================
+Find CC result Page report text spacing changes - Done
+Profile page responive view design - Done
+My account page responive view design - Done</t>
+  </si>
+  <si>
+    <t>Congressional Communities
+==================================
+Find CC page responive view design - Done
+My account page responive view design changes - Done
+About us page responive view design - Done</t>
+  </si>
+  <si>
+    <t>FEFundInfo
+=======================
+KT session
+Discussed with clients and teams</t>
+  </si>
+  <si>
+    <t>FEFundInfo
+=======================
+412359: Invesco Theme - Equity - 2 pdf (3 changes) done
+Discussed with clients</t>
+  </si>
+  <si>
+    <t>FEFundInfo
+=========================
+365013: [PRIIPsEU - MP/PP templates] [Nuveen-PT2092] - creation of new themes for Monthly Performance and Past Performance templates - 7pdf - Done
+Discussed with clients</t>
+  </si>
+  <si>
+    <t>FEFundInfo
+=========================
+498940: Plus Documents 01178633 – Incorrect Page Labels &amp; Font issue (NTAM) - 2PDf - Done 
+Discussed with clients BA</t>
+  </si>
+  <si>
+    <t>FEFundInfo
+=========================
+Product Backlog Item 464481: Plus Documents PT-3097 Creation of new theme (Scottish Widows)
+Product Backlog Item 499375: +Docs - PT-2348 Phoenix -  Amendments to new TargetDatedFund ESG Factsheet</t>
+  </si>
+  <si>
+    <t>FEFundInfo
+=========================
+Product Backlog Item 499375: +Docs - PT-2348 Phoenix -  Amendments to new TargetDatedFund ESG Factsheet
+Product Backlog Item 499391: +Docs - PT-2348 Phoenix -  Amendments to new BlendedWithInsert ESG Factsheet</t>
+  </si>
+  <si>
+    <t>FEFundInfo
+=========================
+Product Backlog Item 499415: +Docs - PT-2348 Phoenix -  Amendments to new BlendedSingleV2WithInsert ESG Factsheet
+Product Backlog Item 499391: +Docs - PT-2348 Phoenix -  Amendments to new BlendedWithInsert ESG Factsheet</t>
   </si>
 </sst>
 </file>
@@ -358,6 +428,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="15" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="15" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -366,32 +445,20 @@
     <xf numFmtId="15" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="15" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -406,8 +473,11 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -808,25 +878,25 @@
   <sheetData>
     <row r="1" spans="2:9" ht="17.25" thickBot="1"/>
     <row r="2" spans="2:9" ht="59.1" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="28"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="4" spans="2:9" ht="30" customHeight="1">
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
       <c r="G4" s="3" t="s">
         <v>2</v>
       </c>
@@ -838,11 +908,11 @@
       <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="28">
         <v>9025475571</v>
       </c>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
       <c r="G5" s="3" t="s">
         <v>4</v>
       </c>
@@ -854,11 +924,11 @@
       <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
     </row>
     <row r="8" spans="2:9" ht="30" customHeight="1">
       <c r="B8" s="5" t="s">
@@ -867,13 +937,13 @@
       <c r="C8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="33"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="32"/>
       <c r="I8" s="7" t="s">
         <v>9</v>
       </c>
@@ -885,13 +955,13 @@
       <c r="C9" s="8">
         <v>8.5</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="19"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="22"/>
       <c r="I9" s="14"/>
     </row>
     <row r="10" spans="2:9" ht="105.75" customHeight="1">
@@ -901,13 +971,13 @@
       <c r="C10" s="8">
         <v>8.5</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="19"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="22"/>
       <c r="I10" s="14"/>
     </row>
     <row r="11" spans="2:9" ht="23.25" customHeight="1">
@@ -917,13 +987,13 @@
       <c r="C11" s="8">
         <v>0</v>
       </c>
-      <c r="D11" s="34" t="s">
+      <c r="D11" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="19"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="22"/>
       <c r="I11" s="14"/>
     </row>
     <row r="12" spans="2:9" ht="18.75" customHeight="1">
@@ -933,13 +1003,13 @@
       <c r="C12" s="8">
         <v>0</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="19"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="22"/>
       <c r="I12" s="14"/>
     </row>
     <row r="13" spans="2:9" ht="102" customHeight="1">
@@ -949,217 +1019,285 @@
       <c r="C13" s="8">
         <v>8.5</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="19"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="22"/>
       <c r="I13" s="14"/>
     </row>
-    <row r="14" spans="2:9" ht="50.25" customHeight="1">
+    <row r="14" spans="2:9" ht="90.75" customHeight="1">
       <c r="B14" s="7">
         <v>45783</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="19"/>
+      <c r="C14" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="22"/>
       <c r="I14" s="14"/>
     </row>
-    <row r="15" spans="2:9" ht="53.25" customHeight="1">
+    <row r="15" spans="2:9" ht="96" customHeight="1">
       <c r="B15" s="7">
         <v>45784</v>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="19"/>
+      <c r="C15" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="22"/>
       <c r="I15" s="14"/>
     </row>
-    <row r="16" spans="2:9" ht="54" customHeight="1">
+    <row r="16" spans="2:9" ht="94.5" customHeight="1">
       <c r="B16" s="7">
         <v>45785</v>
       </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="19"/>
+      <c r="C16" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="22"/>
       <c r="I16" s="14"/>
     </row>
-    <row r="17" spans="2:9" ht="72" customHeight="1">
+    <row r="17" spans="2:9" ht="93" customHeight="1">
       <c r="B17" s="7">
         <v>45786</v>
       </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="19"/>
+      <c r="C17" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="22"/>
       <c r="I17" s="14"/>
     </row>
-    <row r="18" spans="2:9" ht="75.75" customHeight="1">
+    <row r="18" spans="2:9" ht="22.5" customHeight="1">
       <c r="B18" s="7">
         <v>45787</v>
       </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="19"/>
+      <c r="C18" s="8">
+        <v>0</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="22"/>
       <c r="I18" s="14"/>
     </row>
-    <row r="19" spans="2:9" ht="72.75" customHeight="1">
+    <row r="19" spans="2:9" ht="18.75" customHeight="1">
       <c r="B19" s="7">
         <v>45788</v>
       </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="19"/>
+      <c r="C19" s="8">
+        <v>0</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="22"/>
       <c r="I19" s="14"/>
     </row>
-    <row r="20" spans="2:9" ht="66" customHeight="1">
+    <row r="20" spans="2:9" ht="77.25" customHeight="1">
       <c r="B20" s="7">
         <v>45789</v>
       </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="19"/>
+      <c r="C20" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="22"/>
       <c r="I20" s="14"/>
     </row>
-    <row r="21" spans="2:9" ht="54" customHeight="1">
+    <row r="21" spans="2:9" ht="79.5" customHeight="1">
       <c r="B21" s="7">
         <v>45790</v>
       </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="19"/>
+      <c r="C21" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="22"/>
       <c r="I21" s="14"/>
     </row>
-    <row r="22" spans="2:9" ht="55.5" customHeight="1">
+    <row r="22" spans="2:9" ht="90.75" customHeight="1">
       <c r="B22" s="7">
         <v>45791</v>
       </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="19"/>
+      <c r="C22" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="22"/>
       <c r="I22" s="14"/>
     </row>
     <row r="23" spans="2:9" ht="67.5" customHeight="1">
       <c r="B23" s="7">
         <v>45792</v>
       </c>
-      <c r="C23" s="8"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="19"/>
+      <c r="C23" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="22"/>
       <c r="I23" s="14"/>
     </row>
-    <row r="24" spans="2:9" ht="56.25" customHeight="1">
+    <row r="24" spans="2:9" ht="75" customHeight="1">
       <c r="B24" s="7">
         <v>45793</v>
       </c>
-      <c r="C24" s="8"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="19"/>
+      <c r="C24" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="22"/>
       <c r="I24" s="14"/>
     </row>
-    <row r="25" spans="2:9" ht="87" customHeight="1">
+    <row r="25" spans="2:9" ht="22.5" customHeight="1">
       <c r="B25" s="7">
         <v>45794</v>
       </c>
-      <c r="C25" s="8"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="19"/>
+      <c r="C25" s="8">
+        <v>0</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="22"/>
       <c r="I25" s="14"/>
     </row>
-    <row r="26" spans="2:9" ht="85.5" customHeight="1">
+    <row r="26" spans="2:9" ht="23.25" customHeight="1">
       <c r="B26" s="7">
         <v>45795</v>
       </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="19"/>
+      <c r="C26" s="8">
+        <v>0</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="22"/>
       <c r="I26" s="14"/>
     </row>
-    <row r="27" spans="2:9" ht="51" customHeight="1">
+    <row r="27" spans="2:9" ht="72.75" customHeight="1">
       <c r="B27" s="7">
         <v>45796</v>
       </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="19"/>
+      <c r="C27" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="22"/>
       <c r="I27" s="14"/>
     </row>
-    <row r="28" spans="2:9" ht="89.25" customHeight="1">
+    <row r="28" spans="2:9" ht="72" customHeight="1">
       <c r="B28" s="7">
         <v>45797</v>
       </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="19"/>
+      <c r="C28" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="22"/>
       <c r="I28" s="14"/>
     </row>
-    <row r="29" spans="2:9" ht="56.25" customHeight="1">
+    <row r="29" spans="2:9" ht="73.5" customHeight="1">
       <c r="B29" s="7">
         <v>45798</v>
       </c>
-      <c r="C29" s="8"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="19"/>
+      <c r="C29" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="22"/>
       <c r="I29" s="14"/>
     </row>
-    <row r="30" spans="2:9" ht="20.25" customHeight="1">
+    <row r="30" spans="2:9" ht="70.5" customHeight="1">
       <c r="B30" s="7">
         <v>45799</v>
       </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="19"/>
+      <c r="C30" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="22"/>
       <c r="I30" s="14"/>
     </row>
     <row r="31" spans="2:9" ht="18" customHeight="1">
@@ -1167,11 +1305,11 @@
         <v>45800</v>
       </c>
       <c r="C31" s="8"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="19"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="22"/>
       <c r="I31" s="14"/>
     </row>
     <row r="32" spans="2:9" ht="52.5" customHeight="1">
@@ -1179,11 +1317,11 @@
         <v>45801</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="19"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="22"/>
       <c r="I32" s="14"/>
     </row>
     <row r="33" spans="2:9" ht="53.25" customHeight="1">
@@ -1191,11 +1329,11 @@
         <v>45802</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="19"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="22"/>
       <c r="I33" s="14"/>
     </row>
     <row r="34" spans="2:9" ht="87.75" customHeight="1">
@@ -1203,11 +1341,11 @@
         <v>45803</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="19"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="22"/>
       <c r="I34" s="14"/>
     </row>
     <row r="35" spans="2:9" ht="52.5" customHeight="1">
@@ -1215,11 +1353,11 @@
         <v>45804</v>
       </c>
       <c r="C35" s="8"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="19"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="22"/>
       <c r="I35" s="14"/>
     </row>
     <row r="36" spans="2:9" ht="69.75" customHeight="1">
@@ -1227,11 +1365,11 @@
         <v>45805</v>
       </c>
       <c r="C36" s="8"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="19"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="22"/>
       <c r="I36" s="14"/>
     </row>
     <row r="37" spans="2:9" ht="21.75" customHeight="1">
@@ -1239,11 +1377,11 @@
         <v>45806</v>
       </c>
       <c r="C37" s="8"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="21"/>
-      <c r="H37" s="22"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="19"/>
       <c r="I37" s="14"/>
     </row>
     <row r="38" spans="2:9" ht="21" customHeight="1">
@@ -1251,11 +1389,11 @@
         <v>45807</v>
       </c>
       <c r="C38" s="8"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="21"/>
-      <c r="H38" s="22"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="19"/>
       <c r="I38" s="14"/>
     </row>
     <row r="39" spans="2:9" ht="68.25" customHeight="1">
@@ -1263,11 +1401,11 @@
         <v>45808</v>
       </c>
       <c r="C39" s="8"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="19"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="22"/>
       <c r="I39" s="14"/>
     </row>
     <row r="40" spans="2:9" ht="30" customHeight="1">
@@ -1276,24 +1414,24 @@
       </c>
       <c r="C40" s="10">
         <f>SUM(C9:C39)</f>
-        <v>25.5</v>
-      </c>
-      <c r="D40" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="D40" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
-      <c r="H40" s="25"/>
+      <c r="E40" s="34"/>
+      <c r="F40" s="34"/>
+      <c r="G40" s="34"/>
+      <c r="H40" s="34"/>
     </row>
     <row r="42" spans="2:9" ht="30" customHeight="1">
-      <c r="B42" s="23" t="s">
+      <c r="B42" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="C42" s="23"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
+      <c r="C42" s="33"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="27"/>
       <c r="G42" s="16" t="s">
         <v>12</v>
       </c>
@@ -1305,13 +1443,13 @@
       <c r="B43" s="12"/>
     </row>
     <row r="44" spans="2:9" ht="30" customHeight="1">
-      <c r="B44" s="23" t="s">
+      <c r="B44" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="C44" s="23"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="24"/>
+      <c r="C44" s="33"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="27"/>
       <c r="G44" s="16" t="s">
         <v>12</v>
       </c>
@@ -1321,13 +1459,13 @@
       <c r="B45" s="12"/>
     </row>
     <row r="46" spans="2:9" ht="30" customHeight="1">
-      <c r="B46" s="23" t="s">
+      <c r="B46" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="C46" s="23"/>
-      <c r="D46" s="24"/>
-      <c r="E46" s="24"/>
-      <c r="F46" s="24"/>
+      <c r="C46" s="33"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="27"/>
       <c r="G46" s="16" t="s">
         <v>12</v>
       </c>
@@ -1335,33 +1473,6 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:F42"/>
     <mergeCell ref="D39:H39"/>
     <mergeCell ref="D20:H20"/>
     <mergeCell ref="D21:H21"/>
@@ -1378,6 +1489,33 @@
     <mergeCell ref="D38:H38"/>
     <mergeCell ref="D28:H28"/>
     <mergeCell ref="D29:H29"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
@@ -1391,12 +1529,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1514,15 +1649,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DBB90D6-6CF2-454A-903E-412076510F41}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2557F9BC-8CE0-4467-BBA0-44089D18E7E7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1544,10 +1683,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2557F9BC-8CE0-4467-BBA0-44089D18E7E7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DBB90D6-6CF2-454A-903E-412076510F41}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Hemapreetha_Timesheet_1May-31May.xlsx
+++ b/Hemapreetha_Timesheet_1May-31May.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gunas\Hema\git-my\vinove\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93BE19B4-410A-429E-8BCA-233E4F8E0CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E26F7124-690C-4660-BFE8-4125BB0307EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
   <si>
     <t>Monthly Timesheet</t>
   </si>
@@ -191,6 +191,18 @@
 =========================
 Product Backlog Item 499415: +Docs - PT-2348 Phoenix -  Amendments to new BlendedSingleV2WithInsert ESG Factsheet
 Product Backlog Item 499391: +Docs - PT-2348 Phoenix -  Amendments to new BlendedWithInsert ESG Factsheet</t>
+  </si>
+  <si>
+    <t>FEFundInfo
+=========================
+Product Backlog Item 499391: +Docs - PT-2348 Phoenix -  Amendments to new BlendedWithInsert ESG Factsheet
+Product Backlog Item 464481: Plus Documents PT-3097 Creation of new theme (Scottish Widows)</t>
+  </si>
+  <si>
+    <t>FEFundInfo
+=========================
+Product Backlog Item 499375: +Docs - PT-2348 Phoenix -  Amendments to new TargetDatedFund ESG Factsheet
+Product Backlog Item 499669: [pF][Nuveen] PRIIPs KID - New Theme for UK Version (Fusion ID 01188732)</t>
   </si>
 </sst>
 </file>
@@ -428,6 +440,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="15" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="15" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -436,17 +457,14 @@
     <xf numFmtId="15" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="15" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
@@ -456,9 +474,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -473,11 +488,8 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -878,25 +890,25 @@
   <sheetData>
     <row r="1" spans="2:9" ht="17.25" thickBot="1"/>
     <row r="2" spans="2:9" ht="59.1" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="26"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="4" spans="2:9" ht="30" customHeight="1">
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
       <c r="G4" s="3" t="s">
         <v>2</v>
       </c>
@@ -908,11 +920,11 @@
       <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="29">
         <v>9025475571</v>
       </c>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
       <c r="G5" s="3" t="s">
         <v>4</v>
       </c>
@@ -924,11 +936,11 @@
       <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
     </row>
     <row r="8" spans="2:9" ht="30" customHeight="1">
       <c r="B8" s="5" t="s">
@@ -937,13 +949,13 @@
       <c r="C8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="33"/>
       <c r="I8" s="7" t="s">
         <v>9</v>
       </c>
@@ -955,13 +967,13 @@
       <c r="C9" s="8">
         <v>8.5</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="22"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="19"/>
       <c r="I9" s="14"/>
     </row>
     <row r="10" spans="2:9" ht="105.75" customHeight="1">
@@ -971,13 +983,13 @@
       <c r="C10" s="8">
         <v>8.5</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="22"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="19"/>
       <c r="I10" s="14"/>
     </row>
     <row r="11" spans="2:9" ht="23.25" customHeight="1">
@@ -987,13 +999,13 @@
       <c r="C11" s="8">
         <v>0</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="22"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="19"/>
       <c r="I11" s="14"/>
     </row>
     <row r="12" spans="2:9" ht="18.75" customHeight="1">
@@ -1003,13 +1015,13 @@
       <c r="C12" s="8">
         <v>0</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="22"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="19"/>
       <c r="I12" s="14"/>
     </row>
     <row r="13" spans="2:9" ht="102" customHeight="1">
@@ -1019,13 +1031,13 @@
       <c r="C13" s="8">
         <v>8.5</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="22"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="19"/>
       <c r="I13" s="14"/>
     </row>
     <row r="14" spans="2:9" ht="90.75" customHeight="1">
@@ -1035,13 +1047,13 @@
       <c r="C14" s="8">
         <v>8.5</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="22"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="19"/>
       <c r="I14" s="14"/>
     </row>
     <row r="15" spans="2:9" ht="96" customHeight="1">
@@ -1051,13 +1063,13 @@
       <c r="C15" s="8">
         <v>8.5</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="22"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="19"/>
       <c r="I15" s="14"/>
     </row>
     <row r="16" spans="2:9" ht="94.5" customHeight="1">
@@ -1067,13 +1079,13 @@
       <c r="C16" s="8">
         <v>8.5</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="22"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="19"/>
       <c r="I16" s="14"/>
     </row>
     <row r="17" spans="2:9" ht="93" customHeight="1">
@@ -1083,13 +1095,13 @@
       <c r="C17" s="8">
         <v>8.5</v>
       </c>
-      <c r="D17" s="20" t="s">
+      <c r="D17" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="22"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="19"/>
       <c r="I17" s="14"/>
     </row>
     <row r="18" spans="2:9" ht="22.5" customHeight="1">
@@ -1099,13 +1111,13 @@
       <c r="C18" s="8">
         <v>0</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="22"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="19"/>
       <c r="I18" s="14"/>
     </row>
     <row r="19" spans="2:9" ht="18.75" customHeight="1">
@@ -1115,13 +1127,13 @@
       <c r="C19" s="8">
         <v>0</v>
       </c>
-      <c r="D19" s="20" t="s">
+      <c r="D19" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="22"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="19"/>
       <c r="I19" s="14"/>
     </row>
     <row r="20" spans="2:9" ht="77.25" customHeight="1">
@@ -1131,13 +1143,13 @@
       <c r="C20" s="8">
         <v>8.5</v>
       </c>
-      <c r="D20" s="20" t="s">
+      <c r="D20" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="22"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="19"/>
       <c r="I20" s="14"/>
     </row>
     <row r="21" spans="2:9" ht="79.5" customHeight="1">
@@ -1147,13 +1159,13 @@
       <c r="C21" s="8">
         <v>8.5</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="D21" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="22"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="19"/>
       <c r="I21" s="14"/>
     </row>
     <row r="22" spans="2:9" ht="90.75" customHeight="1">
@@ -1163,13 +1175,13 @@
       <c r="C22" s="8">
         <v>8.5</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="D22" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="22"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="19"/>
       <c r="I22" s="14"/>
     </row>
     <row r="23" spans="2:9" ht="67.5" customHeight="1">
@@ -1179,13 +1191,13 @@
       <c r="C23" s="8">
         <v>8.5</v>
       </c>
-      <c r="D23" s="20" t="s">
+      <c r="D23" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="22"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="19"/>
       <c r="I23" s="14"/>
     </row>
     <row r="24" spans="2:9" ht="75" customHeight="1">
@@ -1195,13 +1207,13 @@
       <c r="C24" s="8">
         <v>8.5</v>
       </c>
-      <c r="D24" s="20" t="s">
+      <c r="D24" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="22"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="19"/>
       <c r="I24" s="14"/>
     </row>
     <row r="25" spans="2:9" ht="22.5" customHeight="1">
@@ -1211,13 +1223,13 @@
       <c r="C25" s="8">
         <v>0</v>
       </c>
-      <c r="D25" s="20" t="s">
+      <c r="D25" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="22"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="19"/>
       <c r="I25" s="14"/>
     </row>
     <row r="26" spans="2:9" ht="23.25" customHeight="1">
@@ -1227,13 +1239,13 @@
       <c r="C26" s="8">
         <v>0</v>
       </c>
-      <c r="D26" s="20" t="s">
+      <c r="D26" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="22"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="19"/>
       <c r="I26" s="14"/>
     </row>
     <row r="27" spans="2:9" ht="72.75" customHeight="1">
@@ -1243,13 +1255,13 @@
       <c r="C27" s="8">
         <v>8.5</v>
       </c>
-      <c r="D27" s="20" t="s">
+      <c r="D27" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="22"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="19"/>
       <c r="I27" s="14"/>
     </row>
     <row r="28" spans="2:9" ht="72" customHeight="1">
@@ -1259,13 +1271,13 @@
       <c r="C28" s="8">
         <v>8.5</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="D28" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="22"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="19"/>
       <c r="I28" s="14"/>
     </row>
     <row r="29" spans="2:9" ht="73.5" customHeight="1">
@@ -1275,13 +1287,13 @@
       <c r="C29" s="8">
         <v>8.5</v>
       </c>
-      <c r="D29" s="20" t="s">
+      <c r="D29" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="22"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="19"/>
       <c r="I29" s="14"/>
     </row>
     <row r="30" spans="2:9" ht="70.5" customHeight="1">
@@ -1291,61 +1303,77 @@
       <c r="C30" s="8">
         <v>8.5</v>
       </c>
-      <c r="D30" s="20" t="s">
+      <c r="D30" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="22"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="19"/>
       <c r="I30" s="14"/>
     </row>
-    <row r="31" spans="2:9" ht="18" customHeight="1">
+    <row r="31" spans="2:9" ht="72.75" customHeight="1">
       <c r="B31" s="7">
         <v>45800</v>
       </c>
-      <c r="C31" s="8"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="22"/>
+      <c r="C31" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="19"/>
       <c r="I31" s="14"/>
     </row>
-    <row r="32" spans="2:9" ht="52.5" customHeight="1">
+    <row r="32" spans="2:9" ht="23.25" customHeight="1">
       <c r="B32" s="7">
         <v>45801</v>
       </c>
-      <c r="C32" s="8"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="22"/>
+      <c r="C32" s="8">
+        <v>0</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="19"/>
       <c r="I32" s="14"/>
     </row>
-    <row r="33" spans="2:9" ht="53.25" customHeight="1">
+    <row r="33" spans="2:9" ht="22.5" customHeight="1">
       <c r="B33" s="7">
         <v>45802</v>
       </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="22"/>
+      <c r="C33" s="8">
+        <v>0</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="19"/>
       <c r="I33" s="14"/>
     </row>
-    <row r="34" spans="2:9" ht="87.75" customHeight="1">
+    <row r="34" spans="2:9" ht="69.75" customHeight="1">
       <c r="B34" s="7">
         <v>45803</v>
       </c>
-      <c r="C34" s="8"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="21"/>
-      <c r="H34" s="22"/>
+      <c r="C34" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="19"/>
       <c r="I34" s="14"/>
     </row>
     <row r="35" spans="2:9" ht="52.5" customHeight="1">
@@ -1353,11 +1381,11 @@
         <v>45804</v>
       </c>
       <c r="C35" s="8"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21"/>
-      <c r="H35" s="22"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="19"/>
       <c r="I35" s="14"/>
     </row>
     <row r="36" spans="2:9" ht="69.75" customHeight="1">
@@ -1365,11 +1393,11 @@
         <v>45805</v>
       </c>
       <c r="C36" s="8"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="21"/>
-      <c r="H36" s="22"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="19"/>
       <c r="I36" s="14"/>
     </row>
     <row r="37" spans="2:9" ht="21.75" customHeight="1">
@@ -1377,11 +1405,11 @@
         <v>45806</v>
       </c>
       <c r="C37" s="8"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="19"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="22"/>
       <c r="I37" s="14"/>
     </row>
     <row r="38" spans="2:9" ht="21" customHeight="1">
@@ -1389,11 +1417,11 @@
         <v>45807</v>
       </c>
       <c r="C38" s="8"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="19"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="22"/>
       <c r="I38" s="14"/>
     </row>
     <row r="39" spans="2:9" ht="68.25" customHeight="1">
@@ -1401,11 +1429,11 @@
         <v>45808</v>
       </c>
       <c r="C39" s="8"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
-      <c r="G39" s="21"/>
-      <c r="H39" s="22"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="19"/>
       <c r="I39" s="14"/>
     </row>
     <row r="40" spans="2:9" ht="30" customHeight="1">
@@ -1414,24 +1442,24 @@
       </c>
       <c r="C40" s="10">
         <f>SUM(C9:C39)</f>
-        <v>136</v>
-      </c>
-      <c r="D40" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="D40" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="E40" s="34"/>
-      <c r="F40" s="34"/>
-      <c r="G40" s="34"/>
-      <c r="H40" s="34"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="25"/>
+      <c r="H40" s="25"/>
     </row>
     <row r="42" spans="2:9" ht="30" customHeight="1">
-      <c r="B42" s="33" t="s">
+      <c r="B42" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C42" s="33"/>
-      <c r="D42" s="27"/>
-      <c r="E42" s="27"/>
-      <c r="F42" s="27"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
       <c r="G42" s="16" t="s">
         <v>12</v>
       </c>
@@ -1443,13 +1471,13 @@
       <c r="B43" s="12"/>
     </row>
     <row r="44" spans="2:9" ht="30" customHeight="1">
-      <c r="B44" s="33" t="s">
+      <c r="B44" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C44" s="33"/>
-      <c r="D44" s="27"/>
-      <c r="E44" s="27"/>
-      <c r="F44" s="27"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="24"/>
+      <c r="F44" s="24"/>
       <c r="G44" s="16" t="s">
         <v>12</v>
       </c>
@@ -1459,13 +1487,13 @@
       <c r="B45" s="12"/>
     </row>
     <row r="46" spans="2:9" ht="30" customHeight="1">
-      <c r="B46" s="33" t="s">
+      <c r="B46" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C46" s="33"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
+      <c r="C46" s="23"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="24"/>
       <c r="G46" s="16" t="s">
         <v>12</v>
       </c>
@@ -1473,6 +1501,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:F42"/>
     <mergeCell ref="D39:H39"/>
     <mergeCell ref="D20:H20"/>
     <mergeCell ref="D21:H21"/>
@@ -1489,33 +1544,6 @@
     <mergeCell ref="D38:H38"/>
     <mergeCell ref="D28:H28"/>
     <mergeCell ref="D29:H29"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
@@ -1529,9 +1557,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1649,19 +1680,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2557F9BC-8CE0-4467-BBA0-44089D18E7E7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DBB90D6-6CF2-454A-903E-412076510F41}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1683,9 +1710,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DBB90D6-6CF2-454A-903E-412076510F41}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2557F9BC-8CE0-4467-BBA0-44089D18E7E7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Hemapreetha_Timesheet_1May-31May.xlsx
+++ b/Hemapreetha_Timesheet_1May-31May.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gunas\Hema\git-my\vinove\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E26F7124-690C-4660-BFE8-4125BB0307EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5C6E7F1-0F34-41C9-AEFF-127BCBF4C0F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="40">
   <si>
     <t>Monthly Timesheet</t>
   </si>
@@ -88,9 +88,6 @@
   </si>
   <si>
     <t>Weekend</t>
-  </si>
-  <si>
-    <t>Limited to 160 hours</t>
   </si>
   <si>
     <t>Congressional Communities
@@ -203,6 +200,30 @@
 =========================
 Product Backlog Item 499375: +Docs - PT-2348 Phoenix -  Amendments to new TargetDatedFund ESG Factsheet
 Product Backlog Item 499669: [pF][Nuveen] PRIIPs KID - New Theme for UK Version (Fusion ID 01188732)</t>
+  </si>
+  <si>
+    <t>FEFundInfo
+=========================
+Product Backlog Item 499391: +Docs - PT-2348 Phoenix -  Amendments to new BlendedWithInsert ESG Factsheet
+Product Backlog Item 499375: +Docs - PT-2348 Phoenix -  Amendments to new TargetDatedFund ESG Factsheet</t>
+  </si>
+  <si>
+    <t>FEFundInfo
+=========================
+Product Backlog Item 499375: +Docs - PT-2348 Phoenix -  Amendments to new TargetDatedFund ESG Factsheet
+Product Backlog Item 499415: +Docs - PT-2348 Phoenix -  Amendments to new BlendedSingleV2WithInsert ESG Factsheet
+Product Backlog Item 499391: +Docs - PT-2348 Phoenix -  Amendments to new BlendedWithInsert ESG Factsheet</t>
+  </si>
+  <si>
+    <t>FEFundInfo
+=========================
+Product Backlog Item 499375: +Docs - PT-2348 Phoenix -  Amendments to new TargetDatedFund ESG Factsheet
+Product Backlog Item 499415: +Docs - PT-2348 Phoenix -  Amendments to new BlendedSingleV2WithInsert ESG Factsheet
+Product Backlog Item 499391: +Docs - PT-2348 Phoenix -  Amendments to new BlendedWithInsert ESG Factsheet
+Product Backlog Item 498965: CR 01148189 - +digi - aegon help text alignment issue</t>
+  </si>
+  <si>
+    <t>Limited to 187 hours</t>
   </si>
 </sst>
 </file>
@@ -440,6 +461,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="15" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="15" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -448,32 +478,20 @@
     <xf numFmtId="15" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="15" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -488,8 +506,11 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -512,56 +533,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>339726</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1743075</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>676275</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9507C697-EC1F-4A6D-986A-C947CE15D1D3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9163686" y="259080"/>
-          <a:ext cx="1403349" cy="600075"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
@@ -589,7 +560,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -890,25 +861,25 @@
   <sheetData>
     <row r="1" spans="2:9" ht="17.25" thickBot="1"/>
     <row r="2" spans="2:9" ht="59.1" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="28"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="4" spans="2:9" ht="30" customHeight="1">
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
       <c r="G4" s="3" t="s">
         <v>2</v>
       </c>
@@ -920,27 +891,27 @@
       <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="28">
         <v>9025475571</v>
       </c>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
       <c r="G5" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="30" customHeight="1">
       <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
     </row>
     <row r="8" spans="2:9" ht="30" customHeight="1">
       <c r="B8" s="5" t="s">
@@ -949,13 +920,13 @@
       <c r="C8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="33"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="32"/>
       <c r="I8" s="7" t="s">
         <v>9</v>
       </c>
@@ -967,13 +938,13 @@
       <c r="C9" s="8">
         <v>8.5</v>
       </c>
-      <c r="D9" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="19"/>
+      <c r="D9" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="22"/>
       <c r="I9" s="14"/>
     </row>
     <row r="10" spans="2:9" ht="105.75" customHeight="1">
@@ -983,13 +954,13 @@
       <c r="C10" s="8">
         <v>8.5</v>
       </c>
-      <c r="D10" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="19"/>
+      <c r="D10" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="22"/>
       <c r="I10" s="14"/>
     </row>
     <row r="11" spans="2:9" ht="23.25" customHeight="1">
@@ -999,13 +970,13 @@
       <c r="C11" s="8">
         <v>0</v>
       </c>
-      <c r="D11" s="34" t="s">
+      <c r="D11" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="19"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="22"/>
       <c r="I11" s="14"/>
     </row>
     <row r="12" spans="2:9" ht="18.75" customHeight="1">
@@ -1015,13 +986,13 @@
       <c r="C12" s="8">
         <v>0</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="19"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="22"/>
       <c r="I12" s="14"/>
     </row>
     <row r="13" spans="2:9" ht="102" customHeight="1">
@@ -1031,13 +1002,13 @@
       <c r="C13" s="8">
         <v>8.5</v>
       </c>
-      <c r="D13" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="19"/>
+      <c r="D13" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="22"/>
       <c r="I13" s="14"/>
     </row>
     <row r="14" spans="2:9" ht="90.75" customHeight="1">
@@ -1047,13 +1018,13 @@
       <c r="C14" s="8">
         <v>8.5</v>
       </c>
-      <c r="D14" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="19"/>
+      <c r="D14" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="22"/>
       <c r="I14" s="14"/>
     </row>
     <row r="15" spans="2:9" ht="96" customHeight="1">
@@ -1063,13 +1034,13 @@
       <c r="C15" s="8">
         <v>8.5</v>
       </c>
-      <c r="D15" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="19"/>
+      <c r="D15" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="22"/>
       <c r="I15" s="14"/>
     </row>
     <row r="16" spans="2:9" ht="94.5" customHeight="1">
@@ -1079,13 +1050,13 @@
       <c r="C16" s="8">
         <v>8.5</v>
       </c>
-      <c r="D16" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="19"/>
+      <c r="D16" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="22"/>
       <c r="I16" s="14"/>
     </row>
     <row r="17" spans="2:9" ht="93" customHeight="1">
@@ -1095,13 +1066,13 @@
       <c r="C17" s="8">
         <v>8.5</v>
       </c>
-      <c r="D17" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="19"/>
+      <c r="D17" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="22"/>
       <c r="I17" s="14"/>
     </row>
     <row r="18" spans="2:9" ht="22.5" customHeight="1">
@@ -1111,13 +1082,13 @@
       <c r="C18" s="8">
         <v>0</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="19"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="22"/>
       <c r="I18" s="14"/>
     </row>
     <row r="19" spans="2:9" ht="18.75" customHeight="1">
@@ -1127,13 +1098,13 @@
       <c r="C19" s="8">
         <v>0</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="19"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="22"/>
       <c r="I19" s="14"/>
     </row>
     <row r="20" spans="2:9" ht="77.25" customHeight="1">
@@ -1143,13 +1114,13 @@
       <c r="C20" s="8">
         <v>8.5</v>
       </c>
-      <c r="D20" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="19"/>
+      <c r="D20" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="22"/>
       <c r="I20" s="14"/>
     </row>
     <row r="21" spans="2:9" ht="79.5" customHeight="1">
@@ -1159,13 +1130,13 @@
       <c r="C21" s="8">
         <v>8.5</v>
       </c>
-      <c r="D21" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="19"/>
+      <c r="D21" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="22"/>
       <c r="I21" s="14"/>
     </row>
     <row r="22" spans="2:9" ht="90.75" customHeight="1">
@@ -1175,13 +1146,13 @@
       <c r="C22" s="8">
         <v>8.5</v>
       </c>
-      <c r="D22" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="19"/>
+      <c r="D22" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="22"/>
       <c r="I22" s="14"/>
     </row>
     <row r="23" spans="2:9" ht="67.5" customHeight="1">
@@ -1191,13 +1162,13 @@
       <c r="C23" s="8">
         <v>8.5</v>
       </c>
-      <c r="D23" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="19"/>
+      <c r="D23" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="22"/>
       <c r="I23" s="14"/>
     </row>
     <row r="24" spans="2:9" ht="75" customHeight="1">
@@ -1207,13 +1178,13 @@
       <c r="C24" s="8">
         <v>8.5</v>
       </c>
-      <c r="D24" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="19"/>
+      <c r="D24" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="22"/>
       <c r="I24" s="14"/>
     </row>
     <row r="25" spans="2:9" ht="22.5" customHeight="1">
@@ -1223,13 +1194,13 @@
       <c r="C25" s="8">
         <v>0</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="19"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="22"/>
       <c r="I25" s="14"/>
     </row>
     <row r="26" spans="2:9" ht="23.25" customHeight="1">
@@ -1239,13 +1210,13 @@
       <c r="C26" s="8">
         <v>0</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="19"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="22"/>
       <c r="I26" s="14"/>
     </row>
     <row r="27" spans="2:9" ht="72.75" customHeight="1">
@@ -1255,13 +1226,13 @@
       <c r="C27" s="8">
         <v>8.5</v>
       </c>
-      <c r="D27" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="19"/>
+      <c r="D27" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="22"/>
       <c r="I27" s="14"/>
     </row>
     <row r="28" spans="2:9" ht="72" customHeight="1">
@@ -1271,13 +1242,13 @@
       <c r="C28" s="8">
         <v>8.5</v>
       </c>
-      <c r="D28" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="19"/>
+      <c r="D28" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="22"/>
       <c r="I28" s="14"/>
     </row>
     <row r="29" spans="2:9" ht="73.5" customHeight="1">
@@ -1287,13 +1258,13 @@
       <c r="C29" s="8">
         <v>8.5</v>
       </c>
-      <c r="D29" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="19"/>
+      <c r="D29" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="22"/>
       <c r="I29" s="14"/>
     </row>
     <row r="30" spans="2:9" ht="70.5" customHeight="1">
@@ -1303,13 +1274,13 @@
       <c r="C30" s="8">
         <v>8.5</v>
       </c>
-      <c r="D30" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="19"/>
+      <c r="D30" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="22"/>
       <c r="I30" s="14"/>
     </row>
     <row r="31" spans="2:9" ht="72.75" customHeight="1">
@@ -1319,13 +1290,13 @@
       <c r="C31" s="8">
         <v>8.5</v>
       </c>
-      <c r="D31" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="19"/>
+      <c r="D31" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="22"/>
       <c r="I31" s="14"/>
     </row>
     <row r="32" spans="2:9" ht="23.25" customHeight="1">
@@ -1335,13 +1306,13 @@
       <c r="C32" s="8">
         <v>0</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="D32" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="19"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="22"/>
       <c r="I32" s="14"/>
     </row>
     <row r="33" spans="2:9" ht="22.5" customHeight="1">
@@ -1351,89 +1322,109 @@
       <c r="C33" s="8">
         <v>0</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="19"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="22"/>
       <c r="I33" s="14"/>
     </row>
-    <row r="34" spans="2:9" ht="69.75" customHeight="1">
+    <row r="34" spans="2:9" ht="76.5" customHeight="1">
       <c r="B34" s="7">
         <v>45803</v>
       </c>
       <c r="C34" s="8">
         <v>8.5</v>
       </c>
-      <c r="D34" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="19"/>
+      <c r="D34" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="22"/>
       <c r="I34" s="14"/>
     </row>
-    <row r="35" spans="2:9" ht="52.5" customHeight="1">
+    <row r="35" spans="2:9" ht="85.5" customHeight="1">
       <c r="B35" s="7">
         <v>45804</v>
       </c>
-      <c r="C35" s="8"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="19"/>
+      <c r="C35" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="22"/>
       <c r="I35" s="14"/>
     </row>
     <row r="36" spans="2:9" ht="69.75" customHeight="1">
       <c r="B36" s="7">
         <v>45805</v>
       </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="19"/>
+      <c r="C36" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="22"/>
       <c r="I36" s="14"/>
     </row>
-    <row r="37" spans="2:9" ht="21.75" customHeight="1">
+    <row r="37" spans="2:9" ht="101.25" customHeight="1">
       <c r="B37" s="7">
         <v>45806</v>
       </c>
-      <c r="C37" s="8"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="21"/>
-      <c r="H37" s="22"/>
+      <c r="C37" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="19"/>
       <c r="I37" s="14"/>
     </row>
-    <row r="38" spans="2:9" ht="21" customHeight="1">
+    <row r="38" spans="2:9" ht="106.5" customHeight="1">
       <c r="B38" s="7">
         <v>45807</v>
       </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="21"/>
-      <c r="H38" s="22"/>
+      <c r="C38" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="19"/>
       <c r="I38" s="14"/>
     </row>
-    <row r="39" spans="2:9" ht="68.25" customHeight="1">
+    <row r="39" spans="2:9" ht="26.25" customHeight="1">
       <c r="B39" s="7">
         <v>45808</v>
       </c>
-      <c r="C39" s="8"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="19"/>
+      <c r="C39" s="8">
+        <v>0</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="22"/>
       <c r="I39" s="14"/>
     </row>
     <row r="40" spans="2:9" ht="30" customHeight="1">
@@ -1442,42 +1433,42 @@
       </c>
       <c r="C40" s="10">
         <f>SUM(C9:C39)</f>
-        <v>153</v>
-      </c>
-      <c r="D40" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
-      <c r="H40" s="25"/>
+        <v>187</v>
+      </c>
+      <c r="D40" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="E40" s="34"/>
+      <c r="F40" s="34"/>
+      <c r="G40" s="34"/>
+      <c r="H40" s="34"/>
     </row>
     <row r="42" spans="2:9" ht="30" customHeight="1">
-      <c r="B42" s="23" t="s">
+      <c r="B42" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="C42" s="23"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
+      <c r="C42" s="33"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="27"/>
       <c r="G42" s="16" t="s">
         <v>12</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="2:9">
       <c r="B43" s="12"/>
     </row>
     <row r="44" spans="2:9" ht="30" customHeight="1">
-      <c r="B44" s="23" t="s">
+      <c r="B44" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="C44" s="23"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="24"/>
+      <c r="C44" s="33"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="27"/>
       <c r="G44" s="16" t="s">
         <v>12</v>
       </c>
@@ -1487,13 +1478,13 @@
       <c r="B45" s="12"/>
     </row>
     <row r="46" spans="2:9" ht="30" customHeight="1">
-      <c r="B46" s="23" t="s">
+      <c r="B46" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="C46" s="23"/>
-      <c r="D46" s="24"/>
-      <c r="E46" s="24"/>
-      <c r="F46" s="24"/>
+      <c r="C46" s="33"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="27"/>
       <c r="G46" s="16" t="s">
         <v>12</v>
       </c>
@@ -1501,33 +1492,6 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:F42"/>
     <mergeCell ref="D39:H39"/>
     <mergeCell ref="D20:H20"/>
     <mergeCell ref="D21:H21"/>
@@ -1544,6 +1508,33 @@
     <mergeCell ref="D38:H38"/>
     <mergeCell ref="D28:H28"/>
     <mergeCell ref="D29:H29"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
@@ -1557,12 +1548,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1680,15 +1668,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DBB90D6-6CF2-454A-903E-412076510F41}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2557F9BC-8CE0-4467-BBA0-44089D18E7E7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1710,10 +1702,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2557F9BC-8CE0-4467-BBA0-44089D18E7E7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DBB90D6-6CF2-454A-903E-412076510F41}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>